--- a/Korp/Filial/2026-08/Integracao_Dominio_Korp_Filial_08-2026.xlsx
+++ b/Korp/Filial/2026-08/Integracao_Dominio_Korp_Filial_08-2026.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -61,11 +61,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,9 +114,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2619,14 +2611,14 @@
           <t>2521</t>
         </is>
       </c>
-      <c r="G44" s="10" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Excluir</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
@@ -2636,7 +2628,7 @@
       </c>
       <c r="J44" s="7" t="inlineStr">
         <is>
-          <t>Consignado da Ana: o extrato fecha em 919,30 (9750 + 9751); provisão (9752) e estorno (9754) se anulam. Sugestão: excluir do TXT</t>
+          <t>Consignado da Ana: o extrato fecha em 919,30 (9750 + 9751); provisão (9752) e estorno (9754) se anulam. Excluído do TXT (confirmado)</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr"/>
@@ -2671,14 +2663,14 @@
           <t>2521</t>
         </is>
       </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Excluir</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Excluir</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -2688,7 +2680,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>Lançado no cálculo de férias da Ana, reduzindo o consignado. Sugestão: excluir do TXT</t>
+          <t>Lançado no cálculo de férias da Ana, reduzindo o consignado. Excluído do TXT (confirmado)</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr"/>
@@ -3151,21 +3143,21 @@
       <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="11">
+      <c r="A55" s="10">
         <f>SUM(A5:A54)</f>
         <v/>
       </c>
-      <c r="B55" s="12" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="J55" s="13" t="inlineStr">
+      <c r="J55" s="12" t="inlineStr">
         <is>
           <t>Corrigidos:</t>
         </is>
       </c>
-      <c r="K55" s="12">
+      <c r="K55" s="11">
         <f>COUNTIF(K5:K54,"Sim")&amp;" de "&amp;ROWS(K5:K54)</f>
         <v/>
       </c>

--- a/Korp/Filial/2026-08/Integracao_Dominio_Korp_Filial_08-2026.xlsx
+++ b/Korp/Filial/2026-08/Integracao_Dominio_Korp_Filial_08-2026.xlsx
@@ -3143,9 +3143,8 @@
       <c r="L54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="10">
-        <f>SUM(A5:A54)</f>
-        <v/>
+      <c r="A55" s="10" t="n">
+        <v>67198.62</v>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
